--- a/artfynd/A 48850-2021 artfynd.xlsx
+++ b/artfynd/A 48850-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48850-2021 artfynd.xlsx
+++ b/artfynd/A 48850-2021 artfynd.xlsx
@@ -790,12 +790,7 @@
         <v>81134080</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556284.1106889462</v>
+        <v>556284</v>
       </c>
       <c r="R3" t="n">
-        <v>6945893.949569954</v>
+        <v>6945894</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +860,9 @@
           <t>2019-08-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48850-2021 artfynd.xlsx
+++ b/artfynd/A 48850-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>81134080</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48850-2021 artfynd.xlsx
+++ b/artfynd/A 48850-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>81134080</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48850-2021 artfynd.xlsx
+++ b/artfynd/A 48850-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>81134080</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48850-2021 artfynd.xlsx
+++ b/artfynd/A 48850-2021 artfynd.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+          <t>Erland Lindblad, Anders Granér, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 48850-2021 artfynd.xlsx
+++ b/artfynd/A 48850-2021 artfynd.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Anders Granér, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 48850-2021 artfynd.xlsx
+++ b/artfynd/A 48850-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>81134080</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+          <t>Erland Lindblad, Anders Granér, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 48850-2021 artfynd.xlsx
+++ b/artfynd/A 48850-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>81134080</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Anders Granér, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 48850-2021 artfynd.xlsx
+++ b/artfynd/A 48850-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967390</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967391</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967364</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967369</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967392</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967368</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967362</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134075</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134085</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134079</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967389</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1868,6 +1928,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134074</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967365</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967395</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2171,6 +2246,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967361</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2272,6 +2352,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967370</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2374,6 +2459,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134080</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2476,6 +2566,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134081</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2578,6 +2673,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134084</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2685,6 +2785,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967366</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2782,6 +2887,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134073</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2879,6 +2989,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134083</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2980,6 +3095,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967394</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3077,6 +3197,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134077</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3178,8 +3303,40 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95967363</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>